--- a/data/buffLevel.xlsx
+++ b/data/buffLevel.xlsx
@@ -715,7 +715,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">

--- a/data/buffLevel.xlsx
+++ b/data/buffLevel.xlsx
@@ -103,7 +103,7 @@
     <t/>
   </si>
   <si>
-    <t>atk</t>
+    <t>base_attack</t>
   </si>
   <si>
     <t>bulletCount</t>
@@ -1382,7 +1382,7 @@
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="4" max="4" width="23.4" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
@@ -1517,7 +1517,7 @@
         <v>23</v>
       </c>
       <c r="D5" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>22</v>
@@ -1546,7 +1546,7 @@
         <v>23</v>
       </c>
       <c r="D6" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>22</v>
@@ -1575,7 +1575,7 @@
         <v>23</v>
       </c>
       <c r="D7" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>22</v>
@@ -1778,7 +1778,7 @@
         <v>23</v>
       </c>
       <c r="D14" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>22</v>
@@ -1807,7 +1807,7 @@
         <v>23</v>
       </c>
       <c r="D15" s="13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>22</v>
@@ -1865,7 +1865,7 @@
         <v>26</v>
       </c>
       <c r="D17" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>22</v>

--- a/data/buffLevel.xlsx
+++ b/data/buffLevel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="65">
   <si>
     <t>Id</t>
   </si>
@@ -40,6 +40,9 @@
     <t>buffLevel</t>
   </si>
   <si>
+    <t>desc</t>
+  </si>
+  <si>
     <t>changeAttr1</t>
   </si>
   <si>
@@ -58,6 +61,12 @@
     <t>attrValue3</t>
   </si>
   <si>
+    <t>changeAttr4</t>
+  </si>
+  <si>
+    <t>attrValue4</t>
+  </si>
+  <si>
     <t>specialEffect</t>
   </si>
   <si>
@@ -76,6 +85,9 @@
     <t>Buff等级</t>
   </si>
   <si>
+    <t>技能描述</t>
+  </si>
+  <si>
     <t>改变的属性1</t>
   </si>
   <si>
@@ -94,6 +106,55 @@
     <t>属性3增加值</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>改变的属性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>属性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5B4B00"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加值</t>
+    </r>
+  </si>
+  <si>
     <t>特殊效果key（首版留空）</t>
   </si>
   <si>
@@ -103,16 +164,608 @@
     <t/>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点攻击伤害</t>
+    </r>
+  </si>
+  <si>
     <t>base_attack</t>
   </si>
   <si>
+    <t>提升2点攻击伤害</t>
+  </si>
+  <si>
+    <t>提升3点攻击伤害</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>颗分裂子弹</t>
+    </r>
+  </si>
+  <si>
     <t>bulletCount</t>
   </si>
   <si>
+    <t>增加2颗分裂子弹</t>
+  </si>
+  <si>
+    <t>子弹命中屏幕边界后可额外弹射1次</t>
+  </si>
+  <si>
     <t>ricochetCount</t>
   </si>
   <si>
+    <t>子弹命中屏幕边界后可额外弹射2次</t>
+  </si>
+  <si>
+    <t>子弹命中屏幕边界后可额外弹射3次</t>
+  </si>
+  <si>
+    <t>提升1点攻击伤害，提升5%暴击几率</t>
+  </si>
+  <si>
+    <t>base_crit_rate</t>
+  </si>
+  <si>
+    <t>提升2点攻击伤害，提升10%暴击几率</t>
+  </si>
+  <si>
+    <t>增加1轮射击</t>
+  </si>
+  <si>
     <t>burstCount</t>
+  </si>
+  <si>
+    <t>增加2轮射击</t>
+  </si>
+  <si>
+    <t>提升10%暴击几率</t>
+  </si>
+  <si>
+    <t>提升20%暴击几率</t>
+  </si>
+  <si>
+    <t>提升30%暴击几率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <t>base_crit_dmg</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度</t>
+    </r>
+  </si>
+  <si>
+    <t>base_attack_speed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度，16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度，30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度，60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率，30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率，60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率，90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升1点攻击伤害，提升3%攻击速度，提升5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率，30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -125,7 +778,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -151,10 +804,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF5B4B00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -718,28 +1382,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -748,123 +1403,132 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -890,21 +1554,28 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1376,21 +2047,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="23.4" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="31" customWidth="1"/>
+    <col min="3" max="3" width="62.9" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="23.4" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:9">
+    <row r="1" ht="24" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1415,472 +2089,886 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:9">
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:12">
       <c r="A2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1" spans="1:12">
+      <c r="A3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:12">
+      <c r="A4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="12">
+        <v>1</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="12">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="14.4" spans="1:12">
+      <c r="A5" s="14">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="14">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4" spans="1:12">
+      <c r="A6" s="14">
+        <v>1</v>
+      </c>
+      <c r="B6" s="14">
+        <v>2</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="14">
+        <v>1</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="14">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" ht="14.4" spans="1:12">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="14">
+        <v>3</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" ht="14.4" spans="1:12">
+      <c r="A8" s="14">
+        <v>2</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="14.4" spans="1:12">
+      <c r="A9" s="14">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14">
+        <v>2</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" ht="14.4" spans="1:12">
+      <c r="A10" s="14">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14">
+        <v>1</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" ht="14.4" spans="1:12">
+      <c r="A11" s="14">
+        <v>3</v>
+      </c>
+      <c r="B11" s="14">
+        <v>2</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" ht="14.4" spans="1:12">
+      <c r="A12" s="14">
+        <v>3</v>
+      </c>
+      <c r="B12" s="14">
+        <v>3</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" ht="14.4" spans="1:12">
+      <c r="A13" s="14">
+        <v>4</v>
+      </c>
+      <c r="B13" s="14">
+        <v>1</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" ht="14.4" spans="1:12">
+      <c r="A14" s="14">
+        <v>4</v>
+      </c>
+      <c r="B14" s="14">
+        <v>2</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" ht="14.4" spans="1:12">
+      <c r="A15" s="14">
+        <v>5</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="14">
+        <v>1</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" ht="14.4" spans="1:12">
+      <c r="A16" s="14">
+        <v>5</v>
+      </c>
+      <c r="B16" s="14">
+        <v>2</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="14">
+        <v>1</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" ht="14.4" spans="1:7">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" ht="14.4" spans="1:7">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" ht="14.4" spans="1:7">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" ht="14.4" spans="1:7">
+      <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" ht="14.4" spans="1:7">
+      <c r="A21">
+        <v>7</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" ht="14.4" spans="1:7">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" ht="14.4" spans="1:7">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="24" ht="14.4" spans="1:7">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" ht="14.4" spans="1:7">
+      <c r="A25">
+        <v>8</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="26" ht="14.4" spans="1:7">
+      <c r="A26">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26">
+        <v>0.03</v>
+      </c>
+      <c r="F26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" ht="14.4" spans="1:7">
+      <c r="A27">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27">
+        <v>0.03</v>
+      </c>
+      <c r="F27" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" ht="14.4" spans="1:7">
+      <c r="A28">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28">
+        <v>0.03</v>
+      </c>
+      <c r="F28" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" ht="14.4" spans="1:7">
+      <c r="A29">
+        <v>10</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29">
+        <v>0.03</v>
+      </c>
+      <c r="F29" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="30" ht="14.4" spans="1:7">
+      <c r="A30">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30">
+        <v>0.08</v>
+      </c>
+      <c r="F30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" ht="14.4" spans="1:7">
+      <c r="A31">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31">
+        <v>0.08</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="32" ht="14.4" spans="1:7">
+      <c r="A32">
         <v>11</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" ht="38" customHeight="1" spans="1:9">
-      <c r="A3" s="7" t="s">
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32">
+        <v>0.08</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="33" ht="14.4" spans="1:11">
+      <c r="A33">
         <v>12</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:9">
-      <c r="A4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="11">
+      <c r="B33">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="11">
-        <v>0</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="11">
-        <v>0</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="11">
-        <v>0</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="13">
+      <c r="C33" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="14">
         <v>1</v>
       </c>
-      <c r="B5" s="13">
-        <v>1</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="13">
-        <v>1</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="13">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="13">
-        <v>1</v>
-      </c>
-      <c r="B6" s="13">
-        <v>2</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="13">
-        <v>1</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="13">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="13">
-        <v>0</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="13">
-        <v>1</v>
-      </c>
-      <c r="B7" s="13">
-        <v>3</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="13">
-        <v>1</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="13">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="13">
-        <v>0</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="13">
-        <v>2</v>
-      </c>
-      <c r="B8" s="13">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="13">
-        <v>1</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="13">
-        <v>2</v>
-      </c>
-      <c r="B9" s="13">
-        <v>2</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="13">
-        <v>1</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="13">
-        <v>0</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="13">
-        <v>0</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="13">
-        <v>2</v>
-      </c>
-      <c r="B10" s="13">
-        <v>3</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="13">
-        <v>1</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="13">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="13">
-        <v>3</v>
-      </c>
-      <c r="B11" s="13">
-        <v>1</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="13">
-        <v>1</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="13">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="13">
-        <v>3</v>
-      </c>
-      <c r="B12" s="13">
-        <v>2</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="13">
-        <v>1</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="13">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="13">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="13">
-        <v>3</v>
-      </c>
-      <c r="B13" s="13">
-        <v>3</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="13">
-        <v>1</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="13">
-        <v>0</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="13">
-        <v>4</v>
-      </c>
-      <c r="B14" s="13">
-        <v>1</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="13">
-        <v>2</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="13">
-        <v>4</v>
-      </c>
-      <c r="B15" s="13">
-        <v>2</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="13">
-        <v>2</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="13">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="13">
-        <v>0</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="13">
-        <v>5</v>
-      </c>
-      <c r="B16" s="13">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="13">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="13">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="13">
-        <v>5</v>
-      </c>
-      <c r="B17" s="13">
-        <v>2</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="13">
-        <v>1</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="13">
-        <v>0</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="13">
-        <v>0</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>22</v>
+      <c r="F33" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="H33" t="s">
+        <v>54</v>
+      </c>
+      <c r="I33">
+        <v>0.03</v>
+      </c>
+      <c r="J33" t="s">
+        <v>50</v>
+      </c>
+      <c r="K33">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/buffLevel.xlsx
+++ b/data/buffLevel.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="59">
   <si>
     <t>Id</t>
   </si>
@@ -199,13 +199,38 @@
     <t>提升3点攻击伤害</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>增加</t>
+    <t>子弹命中屏幕边界后可额外弹射1次</t>
+  </si>
+  <si>
+    <t>ricochetCount</t>
+  </si>
+  <si>
+    <t>子弹命中屏幕边界后可额外弹射2次</t>
+  </si>
+  <si>
+    <t>子弹命中屏幕边界后可额外弹射3次</t>
+  </si>
+  <si>
+    <t>提升1点攻击伤害，提升15%暴击几率</t>
+  </si>
+  <si>
+    <t>base_crit_rate</t>
+  </si>
+  <si>
+    <t>提升2点攻击伤害，提升30%暴击几率</t>
+  </si>
+  <si>
+    <t>提升10%暴击几率</t>
+  </si>
+  <si>
+    <t>提升15%暴击几率</t>
+  </si>
+  <si>
+    <t>提升20%暴击几率</t>
+  </si>
+  <si>
+    <r>
+      <t>提升3</t>
     </r>
     <r>
       <rPr>
@@ -213,70 +238,23 @@
         <rFont val="Carlito"/>
         <charset val="134"/>
       </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>颗分裂子弹</t>
-    </r>
-  </si>
-  <si>
-    <t>bulletCount</t>
-  </si>
-  <si>
-    <t>增加2颗分裂子弹</t>
-  </si>
-  <si>
-    <t>子弹命中屏幕边界后可额外弹射1次</t>
-  </si>
-  <si>
-    <t>ricochetCount</t>
-  </si>
-  <si>
-    <t>子弹命中屏幕边界后可额外弹射2次</t>
-  </si>
-  <si>
-    <t>子弹命中屏幕边界后可额外弹射3次</t>
-  </si>
-  <si>
-    <t>提升1点攻击伤害，提升5%暴击几率</t>
-  </si>
-  <si>
-    <t>base_crit_rate</t>
-  </si>
-  <si>
-    <t>提升2点攻击伤害，提升10%暴击几率</t>
-  </si>
-  <si>
-    <t>增加1轮射击</t>
-  </si>
-  <si>
-    <t>burstCount</t>
-  </si>
-  <si>
-    <t>增加2轮射击</t>
-  </si>
-  <si>
-    <t>提升10%暴击几率</t>
-  </si>
-  <si>
-    <t>提升20%暴击几率</t>
-  </si>
-  <si>
-    <t>提升30%暴击几率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升</t>
+      <t>0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <t>base_crit_dmg</t>
+  </si>
+  <si>
+    <r>
+      <t>提升7</t>
     </r>
     <r>
       <rPr>
@@ -284,7 +262,7 @@
         <rFont val="Carlito"/>
         <charset val="134"/>
       </rPr>
-      <t>50%</t>
+      <t>0%</t>
     </r>
     <r>
       <rPr>
@@ -296,15 +274,257 @@
     </r>
   </si>
   <si>
-    <t>base_crit_dmg</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
+    <r>
+      <t>提升12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度</t>
+    </r>
+  </si>
+  <si>
+    <t>base_attack_speed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提升60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>提升15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度，6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>提升25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度，12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>提升15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度，15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>提升25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度，25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>提升10</t>
     </r>
     <r>
@@ -313,7 +533,23 @@
         <rFont val="Carlito"/>
         <charset val="134"/>
       </rPr>
-      <t>0%</t>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率，20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
     </r>
     <r>
       <rPr>
@@ -326,12 +562,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升1</t>
+      <t>提升15</t>
     </r>
     <r>
       <rPr>
@@ -339,7 +570,23 @@
         <rFont val="Carlito"/>
         <charset val="134"/>
       </rPr>
-      <t>50%</t>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率，40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
     </r>
     <r>
       <rPr>
@@ -352,12 +599,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升</t>
+      <t>提升20</t>
     </r>
     <r>
       <rPr>
@@ -365,28 +607,15 @@
         <rFont val="Carlito"/>
         <charset val="134"/>
       </rPr>
-      <t>5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击速度</t>
-    </r>
-  </si>
-  <si>
-    <t>base_attack_speed</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升10</t>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击几率，60</t>
     </r>
     <r>
       <rPr>
@@ -402,17 +631,12 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>攻击速度</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升1</t>
+      <t>暴击伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>提升1点攻击伤害，提升10%攻击速度，提升10</t>
     </r>
     <r>
       <rPr>
@@ -420,74 +644,6 @@
         <rFont val="Carlito"/>
         <charset val="134"/>
       </rPr>
-      <t>5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击速度</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击速度，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击几率</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
       <t>%</t>
     </r>
     <r>
@@ -496,259 +652,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>攻击速度，16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击几率</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击速度，30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击速度，60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击几率，30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击几率，60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升24</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击几率，90</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提升1点攻击伤害，提升3%攻击速度，提升5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>暴击几率，30</t>
+      <t>暴击几率，20</t>
     </r>
     <r>
       <rPr>
@@ -2047,7 +1951,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2386,16 +2290,16 @@
     </row>
     <row r="10" ht="14.4" spans="1:12">
       <c r="A10" s="14">
+        <v>2</v>
+      </c>
+      <c r="B10" s="14">
         <v>3</v>
-      </c>
-      <c r="B10" s="14">
-        <v>1</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E10" s="14">
         <v>1</v>
@@ -2423,22 +2327,22 @@
         <v>3</v>
       </c>
       <c r="B11" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G11" s="14">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>28</v>
@@ -2457,22 +2361,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E12" s="14">
         <v>1</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G12" s="14">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H12" s="14" t="s">
         <v>28</v>
@@ -2487,295 +2391,251 @@
       </c>
     </row>
     <row r="13" ht="14.4" spans="1:12">
-      <c r="A13" s="14">
+      <c r="A13">
         <v>4</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="14">
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" ht="14.4" spans="1:12">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" ht="14.4" spans="1:12">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" ht="14.4" spans="1:12">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="14">
-        <v>0.05</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" ht="14.4" spans="1:12">
-      <c r="A14" s="14">
-        <v>4</v>
-      </c>
-      <c r="B14" s="14">
+      <c r="C16" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" ht="14.4" spans="1:11">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17">
         <v>2</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="14">
-        <v>1</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="14">
-        <v>0.05</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" ht="14.4" spans="1:12">
-      <c r="A15" s="14">
+      <c r="C17" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" ht="14.4" spans="1:11">
+      <c r="A18">
         <v>5</v>
       </c>
-      <c r="B15" s="14">
-        <v>1</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="14" t="s">
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="14">
-        <v>1</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="14">
-        <v>0</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" ht="14.4" spans="1:12">
-      <c r="A16" s="14">
-        <v>5</v>
-      </c>
-      <c r="B16" s="14">
-        <v>2</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="14">
-        <v>1</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="14">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" ht="14.4" spans="1:7">
-      <c r="A17">
-        <v>6</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="18" ht="14.4" spans="1:7">
-      <c r="A18">
-        <v>6</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" t="s">
-        <v>41</v>
-      </c>
       <c r="E18">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="19" ht="14.4" spans="1:7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" ht="14.4" spans="1:11">
       <c r="A19">
         <v>6</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
         <v>48</v>
       </c>
-      <c r="D19" t="s">
-        <v>41</v>
-      </c>
       <c r="E19">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20" ht="14.4" spans="1:7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20" ht="14.4" spans="1:11">
       <c r="A20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>49</v>
       </c>
       <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="21" ht="14.4" spans="1:11">
+      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" ht="14.4" spans="1:7">
-      <c r="A21">
-        <v>7</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" ht="14.4" spans="1:7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="22" ht="14.4" spans="1:11">
       <c r="A22">
         <v>7</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22">
+        <v>0.15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="14.4" spans="1:11">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D22" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" ht="14.4" spans="1:7">
-      <c r="A23">
-        <v>8</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>53</v>
-      </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E23">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="24" ht="14.4" spans="1:7">
+        <v>0.1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" ht="14.4" spans="1:11">
       <c r="A24">
         <v>8</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E24">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="25" ht="14.4" spans="1:7">
+        <v>0.15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="14.4" spans="1:11">
       <c r="A25">
         <v>8</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E25">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="26" ht="14.4" spans="1:7">
+        <v>0.1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" ht="14.4" spans="1:11">
       <c r="A26">
         <v>9</v>
       </c>
@@ -2783,22 +2643,22 @@
         <v>1</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E26">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G26">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" ht="14.4" spans="1:7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27" ht="14.4" spans="1:11">
       <c r="A27">
         <v>9</v>
       </c>
@@ -2806,169 +2666,77 @@
         <v>2</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E27">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G27">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" ht="14.4" spans="1:7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" ht="14.4" spans="1:11">
       <c r="A28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E28">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F28" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G28">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" ht="14.4" spans="1:7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29" ht="14.4" spans="1:11">
       <c r="A29">
         <v>10</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29">
-        <v>0.03</v>
-      </c>
-      <c r="F29" t="s">
-        <v>50</v>
-      </c>
-      <c r="G29">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="30" ht="14.4" spans="1:7">
-      <c r="A30">
-        <v>11</v>
-      </c>
-      <c r="B30">
+        <v>58</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="14">
         <v>1</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30">
-        <v>0.08</v>
-      </c>
-      <c r="F30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G30">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" ht="14.4" spans="1:7">
-      <c r="A31">
-        <v>11</v>
-      </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31">
-        <v>0.08</v>
-      </c>
-      <c r="F31" t="s">
-        <v>50</v>
-      </c>
-      <c r="G31">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="32" ht="14.4" spans="1:7">
-      <c r="A32">
-        <v>11</v>
-      </c>
-      <c r="B32">
-        <v>3</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32">
-        <v>0.08</v>
-      </c>
-      <c r="F32" t="s">
-        <v>50</v>
-      </c>
-      <c r="G32">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="33" ht="14.4" spans="1:11">
-      <c r="A33">
-        <v>12</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="14">
-        <v>1</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G33" s="14">
-        <v>0.05</v>
-      </c>
-      <c r="H33" t="s">
-        <v>54</v>
-      </c>
-      <c r="I33">
-        <v>0.03</v>
-      </c>
-      <c r="J33" t="s">
-        <v>50</v>
-      </c>
-      <c r="K33">
-        <v>0.3</v>
+      <c r="F29" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>48</v>
+      </c>
+      <c r="I29">
+        <v>0.1</v>
+      </c>
+      <c r="J29" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
